--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential FMCG Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential FMCG Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="110">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential FMCG Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -88,36 +88,36 @@
     <t>Food Products</t>
   </si>
   <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Dabur India Ltd.</t>
+  </si>
+  <si>
+    <t>INE016A01026</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Tata Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE192A01025</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
     <t>Godrej Consumer Products Ltd.</t>
   </si>
   <si>
     <t>INE102D01028</t>
   </si>
   <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Tata Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE192A01025</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
-  </si>
-  <si>
     <t>United Breweries Ltd.</t>
   </si>
   <si>
@@ -127,31 +127,46 @@
     <t>Beverages</t>
   </si>
   <si>
+    <t>Amrutanjan Health Care Ltd.</t>
+  </si>
+  <si>
+    <t>INE098F01031</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Marico Ltd.</t>
+  </si>
+  <si>
+    <t>INE196A01026</t>
+  </si>
+  <si>
+    <t>United Spirits Ltd.</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
     <t>Gillette India Ltd.</t>
   </si>
   <si>
     <t>INE322A01010</t>
   </si>
   <si>
-    <t>Amrutanjan Health Care Ltd.</t>
-  </si>
-  <si>
-    <t>INE098F01031</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>Marico Ltd.</t>
-  </si>
-  <si>
-    <t>INE196A01026</t>
-  </si>
-  <si>
-    <t>United Spirits Ltd.</t>
-  </si>
-  <si>
-    <t>INE854D01024</t>
+    <t>Honasa Consumer Ltd.</t>
+  </si>
+  <si>
+    <t>INE0J5401028</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
   </si>
   <si>
     <t>Colgate - Palmolive (India) Ltd.</t>
@@ -160,6 +175,27 @@
     <t>INE259A01022</t>
   </si>
   <si>
+    <t>Jyothy Labs Ltd</t>
+  </si>
+  <si>
+    <t>INE668F01031</t>
+  </si>
+  <si>
+    <t>Household Products</t>
+  </si>
+  <si>
+    <t>Adani Wilmar Ltd</t>
+  </si>
+  <si>
+    <t>INE699H01024</t>
+  </si>
+  <si>
+    <t>Emami Ltd.</t>
+  </si>
+  <si>
+    <t>INE548C01032</t>
+  </si>
+  <si>
     <t>Relaxo Footwears Ltd.</t>
   </si>
   <si>
@@ -169,22 +205,22 @@
     <t>Consumer Durables</t>
   </si>
   <si>
-    <t>Adani Wilmar Ltd</t>
-  </si>
-  <si>
-    <t>INE699H01024</t>
-  </si>
-  <si>
-    <t>Honasa Consumer Ltd.</t>
-  </si>
-  <si>
-    <t>INE0J5401028</t>
-  </si>
-  <si>
-    <t>Emami Ltd.</t>
-  </si>
-  <si>
-    <t>INE548C01032</t>
+    <t>Galaxy Surfactants Ltd.</t>
+  </si>
+  <si>
+    <t>INE600K01018</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Mold-Tek Packaging Ltd</t>
+  </si>
+  <si>
+    <t>INE893J01029</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
   </si>
   <si>
     <t>Procter &amp; Gamble Hygiene and Health Care Ltd.</t>
@@ -193,52 +229,10 @@
     <t>INE179A01014</t>
   </si>
   <si>
-    <t>Galaxy Surfactants Ltd.</t>
-  </si>
-  <si>
-    <t>INE600K01018</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Mold-Tek Packaging Ltd</t>
-  </si>
-  <si>
-    <t>INE893J01029</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Jyothy Labs Ltd</t>
-  </si>
-  <si>
-    <t>INE668F01031</t>
-  </si>
-  <si>
-    <t>Household Products</t>
-  </si>
-  <si>
-    <t>Godfrey Phillips India Ltd.</t>
-  </si>
-  <si>
-    <t>INE260B01028</t>
-  </si>
-  <si>
-    <t>Cigarettes &amp; Tobacco Products</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd. (Covered call) $$</t>
+    <t>Cello World Ltd.</t>
+  </si>
+  <si>
+    <t>INE0LMW01024</t>
   </si>
   <si>
     <t>Foreign Securities/Overseas ETFs</t>
@@ -283,15 +277,24 @@
     <t>Treasury Bills</t>
   </si>
   <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z471</t>
+    <t>91 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
+    <t>182 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Y407</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
+  </si>
+  <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
   </si>
   <si>
@@ -316,9 +319,6 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
-    <t>$$ - Derivatives.</t>
-  </si>
-  <si>
     <t>Industry classification is done as per Global Industry Classification Standard (GICS) by MSCI and Standard &amp; Poor’s for Foreign Equity</t>
   </si>
   <si>
@@ -331,7 +331,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -735,13 +735,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -759,7 +759,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18554700"/>
+          <a:off x="666750" y="18364200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -774,13 +774,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>119</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -798,7 +798,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="21412200"/>
+          <a:off x="666750" y="21221700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1132,12 +1132,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J109"/>
+  <dimension ref="B1:J108"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.571428571428573" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="17.0" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="36.0" collapsed="true"/>
     <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.0" collapsed="true"/>
@@ -1232,10 +1232,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>173570.33000000005</v>
+        <v>184098.90000000002</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9383139258765002</v>
+        <v>0.9083058201051</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1269,10 +1269,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>173570.33000000005</v>
+        <v>184098.90000000002</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9383139258765002</v>
+        <v>0.9083058201051</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1306,10 +1306,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>172768.33000000005</v>
+        <v>183464.06000000003</v>
       </c>
       <c r="H9" s="10">
-        <v>0.9339783475058002</v>
+        <v>0.9051736511088</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1332,13 +1332,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="14">
-        <v>11154691</v>
+        <v>14529718</v>
       </c>
       <c r="G10" s="15">
-        <v>49917.24</v>
+        <v>60741.49</v>
       </c>
       <c r="H10" s="16">
-        <v>0.2698505063243</v>
+        <v>0.2996859236471</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1361,13 +1361,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="14">
-        <v>1429047</v>
+        <v>1481447</v>
       </c>
       <c r="G11" s="15">
-        <v>35280.31</v>
+        <v>34788.82</v>
       </c>
       <c r="H11" s="16">
-        <v>0.1907238764959</v>
+        <v>0.1716408282756</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1390,13 +1390,13 @@
         <v>23</v>
       </c>
       <c r="F12" s="14">
-        <v>754474</v>
+        <v>707127</v>
       </c>
       <c r="G12" s="15">
-        <v>17452.49</v>
+        <v>16944.18</v>
       </c>
       <c r="H12" s="16">
-        <v>0.094347429127</v>
+        <v>0.083599072623</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1416,16 +1416,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F13" s="14">
-        <v>899274</v>
+        <v>180954</v>
       </c>
       <c r="G13" s="15">
-        <v>10083.11</v>
+        <v>9971.47</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0545088698578</v>
+        <v>0.0491971665013</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1436,25 +1436,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F14" s="14">
-        <v>183950</v>
+        <v>1771739</v>
       </c>
       <c r="G14" s="15">
-        <v>9435.99</v>
+        <v>8556.61</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0510105662727</v>
+        <v>0.0422165404756</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1477,13 +1477,13 @@
         <v>31</v>
       </c>
       <c r="F15" s="14">
-        <v>893471</v>
+        <v>674495</v>
       </c>
       <c r="G15" s="15">
-        <v>9154.95</v>
+        <v>7461.94</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0494912758172</v>
+        <v>0.0368156655541</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1503,16 +1503,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F16" s="14">
-        <v>1401410</v>
+        <v>589698</v>
       </c>
       <c r="G16" s="15">
-        <v>7425.37</v>
+        <v>7261.54</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0401412388614</v>
+        <v>0.0358269334848</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1535,13 +1535,13 @@
         <v>36</v>
       </c>
       <c r="F17" s="14">
-        <v>299361</v>
+        <v>323182</v>
       </c>
       <c r="G17" s="15">
-        <v>6424.29</v>
+        <v>6388.66</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0347294423584</v>
+        <v>0.0315203244597</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1561,16 +1561,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F18" s="14">
-        <v>65436</v>
+        <v>713715</v>
       </c>
       <c r="G18" s="15">
-        <v>5632.24</v>
+        <v>5081.65</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0304476532704</v>
+        <v>0.0250718079833</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1581,25 +1581,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F19" s="14">
-        <v>706798</v>
+        <v>609519</v>
       </c>
       <c r="G19" s="15">
-        <v>4709.75</v>
+        <v>4366.9</v>
       </c>
       <c r="H19" s="16">
-        <v>0.025460711012</v>
+        <v>0.0215453796074</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1619,16 +1619,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F20" s="14">
-        <v>659519</v>
+        <v>268117</v>
       </c>
       <c r="G20" s="15">
-        <v>4423.06</v>
+        <v>4075.65</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0239108768934</v>
+        <v>0.0201084124658</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1648,16 +1648,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F21" s="14">
-        <v>178117</v>
+        <v>40672</v>
       </c>
       <c r="G21" s="15">
-        <v>2536.39</v>
+        <v>3832.52</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0137116179848</v>
+        <v>0.0189088594319</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1677,16 +1677,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F22" s="14">
-        <v>79437</v>
+        <v>694726</v>
       </c>
       <c r="G22" s="15">
-        <v>2241.35</v>
+        <v>2198.46</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0121166441163</v>
+        <v>0.010846746033</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1709,13 +1709,13 @@
         <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>256692</v>
+        <v>117346</v>
       </c>
       <c r="G23" s="15">
-        <v>1410.39</v>
+        <v>2178.18</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0076245091999</v>
+        <v>0.0107466887158</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1735,16 +1735,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F24" s="14">
-        <v>480000</v>
+        <v>79437</v>
       </c>
       <c r="G24" s="15">
-        <v>1279.92</v>
+        <v>1950.89</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0069191938507</v>
+        <v>0.0096252869592</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1764,16 +1764,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F25" s="14">
-        <v>450547</v>
+        <v>414939</v>
       </c>
       <c r="G25" s="15">
-        <v>991.65</v>
+        <v>1431.54</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0053608183184</v>
+        <v>0.0070629216889</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1784,25 +1784,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F26" s="14">
-        <v>160000</v>
+        <v>480000</v>
       </c>
       <c r="G26" s="15">
-        <v>943.44</v>
+        <v>1320</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0051001970799</v>
+        <v>0.0065126064443</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1813,25 +1813,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F27" s="14">
-        <v>5945</v>
+        <v>200000</v>
       </c>
       <c r="G27" s="15">
-        <v>862.06</v>
+        <v>1168.4</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0046602602123</v>
+        <v>0.0057646434618</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1842,25 +1842,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F28" s="14">
-        <v>35966</v>
+        <v>256692</v>
       </c>
       <c r="G28" s="15">
-        <v>858.62</v>
+        <v>1121.87</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0046416637165</v>
+        <v>0.0055350740846</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1871,25 +1871,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F29" s="14">
-        <v>417255</v>
+        <v>46617</v>
       </c>
       <c r="G29" s="15">
-        <v>679.92</v>
+        <v>1075.03</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0036756190097</v>
+        <v>0.0053039752317</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1900,25 +1900,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F30" s="14">
         <v>105193</v>
       </c>
       <c r="G30" s="15">
-        <v>580.51</v>
+        <v>703.69</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0031382127182</v>
+        <v>0.0034718606279</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1929,25 +1929,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="F31" s="14">
-        <v>85643</v>
+        <v>4810</v>
       </c>
       <c r="G31" s="15">
-        <v>341.20</v>
+        <v>653.39</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0018445128928</v>
+        <v>0.003223690852</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1967,16 +1967,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F32" s="14">
-        <v>4321</v>
+        <v>31033</v>
       </c>
       <c r="G32" s="15">
-        <v>195.20</v>
+        <v>191.18</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0010552430149</v>
+        <v>0.0009432425</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -1987,25 +1987,6 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="14">
-        <v>-12500</v>
-      </c>
-      <c r="G33" s="15">
-        <v>-14.80</v>
-      </c>
-      <c r="H33" s="16">
-        <v>-0.0000800081794</v>
-      </c>
-      <c r="I33" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="11" t="s">
@@ -2013,26 +1994,28 @@
       </c>
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
-      <c r="B34" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="14">
-        <v>-35000</v>
-      </c>
-      <c r="G34" s="15">
-        <v>-76.32</v>
-      </c>
-      <c r="H34" s="16">
-        <v>-0.0004125827197</v>
-      </c>
-      <c r="I34" s="15" t="s">
+      <c r="B34" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="9">
+        <v>634.84</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0.0031321689963</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="11" t="s">
@@ -2041,6 +2024,27 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="14">
+        <v>11095</v>
+      </c>
+      <c r="G35" s="15">
+        <v>634.84</v>
+      </c>
+      <c r="H35" s="16">
+        <v>0.0031321689963</v>
+      </c>
+      <c r="I35" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J35" s="11" t="s">
@@ -2048,28 +2052,7 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
-      <c r="B36" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="9">
-        <v>802</v>
-      </c>
-      <c r="H36" s="10">
-        <v>0.0043355783707</v>
-      </c>
-      <c r="I36" s="9" t="s">
+      <c r="B36" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J36" s="11" t="s">
@@ -2077,28 +2060,28 @@
       </c>
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="14">
-        <v>11095</v>
-      </c>
-      <c r="G37" s="15">
-        <v>802</v>
-      </c>
-      <c r="H37" s="16">
-        <v>0.0043355783707</v>
-      </c>
-      <c r="I37" s="15" t="s">
+      <c r="H37" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="11" t="s">
@@ -2130,10 +2113,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>13</v>
@@ -2152,7 +2135,7 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="7" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>13</v>
@@ -2167,10 +2150,10 @@
         <v>13</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>13</v>
@@ -2189,7 +2172,7 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="7" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>13</v>
@@ -2204,10 +2187,10 @@
         <v>13</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>13</v>
@@ -2226,7 +2209,7 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>13</v>
@@ -2241,10 +2224,10 @@
         <v>13</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>13</v>
@@ -2263,7 +2246,7 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>13</v>
@@ -2278,10 +2261,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>13</v>
@@ -2300,7 +2283,7 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>13</v>
@@ -2315,10 +2298,10 @@
         <v>13</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>13</v>
@@ -2337,7 +2320,7 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>13</v>
@@ -2351,11 +2334,11 @@
       <c r="F51" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>79</v>
+      <c r="G51" s="9">
+        <v>3974.22</v>
+      </c>
+      <c r="H51" s="10">
+        <v>0.019607977866100003</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>13</v>
@@ -2374,7 +2357,7 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>13</v>
@@ -2388,11 +2371,11 @@
       <c r="F53" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G53" s="9">
-        <v>499.56</v>
-      </c>
-      <c r="H53" s="10">
-        <v>0.0027006004125</v>
+      <c r="G53" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>13</v>
@@ -2411,7 +2394,7 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>13</v>
@@ -2426,10 +2409,10 @@
         <v>13</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I55" s="9" t="s">
         <v>13</v>
@@ -2448,7 +2431,7 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>13</v>
@@ -2462,11 +2445,11 @@
       <c r="F57" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>79</v>
+      <c r="G57" s="9">
+        <v>3974.22</v>
+      </c>
+      <c r="H57" s="10">
+        <v>0.019607977866100003</v>
       </c>
       <c r="I57" s="9" t="s">
         <v>13</v>
@@ -2477,36 +2460,57 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>13</v>
+        <v>87</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F58" s="14">
+        <v>2500000</v>
+      </c>
+      <c r="G58" s="15">
+        <v>2484.75</v>
+      </c>
+      <c r="H58" s="16">
+        <v>0.0122592415626</v>
+      </c>
+      <c r="I58" s="15">
+        <v>5.60</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="9">
-        <v>499.56</v>
-      </c>
-      <c r="H59" s="10">
-        <v>0.0027006004125</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>13</v>
+      <c r="B59" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F59" s="14">
+        <v>1350000</v>
+      </c>
+      <c r="G59" s="15">
+        <v>1340.52</v>
+      </c>
+      <c r="H59" s="16">
+        <v>0.0066138478718</v>
+      </c>
+      <c r="I59" s="15">
+        <v>5.61</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -2514,28 +2518,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>91</v>
-      </c>
       <c r="F60" s="14">
-        <v>500000</v>
+        <v>150000</v>
       </c>
       <c r="G60" s="15">
-        <v>499.56</v>
+        <v>148.95</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0027006004125</v>
+        <v>0.0007348884317</v>
       </c>
       <c r="I60" s="15">
-        <v>6.37</v>
+        <v>5.61</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -2551,7 +2555,7 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>13</v>
@@ -2566,10 +2570,10 @@
         <v>13</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>13</v>
@@ -2588,7 +2592,7 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>13</v>
@@ -2603,10 +2607,10 @@
         <v>13</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I64" s="9" t="s">
         <v>13</v>
@@ -2625,7 +2629,7 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>13</v>
@@ -2640,10 +2644,10 @@
         <v>13</v>
       </c>
       <c r="G66" s="9">
-        <v>9793.10</v>
+        <v>16120.96</v>
       </c>
       <c r="H66" s="10">
-        <v>0.052941087958399996</v>
+        <v>0.0795374757464</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>13</v>
@@ -2662,7 +2666,7 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>13</v>
@@ -2680,7 +2684,7 @@
         <v>1273.20682</v>
       </c>
       <c r="H68" s="10">
-        <v>0.0068829026811</v>
+        <v>0.0062817385916</v>
       </c>
       <c r="I68" s="9" t="s">
         <v>13</v>
@@ -2691,7 +2695,7 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69" s="13"/>
       <c r="D69" s="13" t="s">
@@ -2702,7 +2706,7 @@
         <v>1273.20682</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0068829026811</v>
+        <v>0.0062817385916</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -2721,7 +2725,7 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C71" s="18" t="s">
         <v>13</v>
@@ -2736,10 +2740,10 @@
         <v>13</v>
       </c>
       <c r="G71" s="18">
-        <v>-155.10977321007522</v>
+        <v>-2783.459495779971</v>
       </c>
       <c r="H71" s="19">
-        <v>-0.0008385169299542554</v>
+        <v>-0.013733012310486192</v>
       </c>
       <c r="I71" s="18" t="s">
         <v>13</v>
@@ -2750,7 +2754,7 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C72" s="18" t="s">
         <v>13</v>
@@ -2765,10 +2769,10 @@
         <v>13</v>
       </c>
       <c r="G72" s="18">
-        <v>184981.08704679</v>
+        <v>202683.82732422</v>
       </c>
       <c r="H72" s="19">
-        <v>0.9999999999985456</v>
+        <v>0.9999999999987135</v>
       </c>
       <c r="I72" s="18" t="s">
         <v>13</v>
@@ -2779,7 +2783,7 @@
     </row>
     <row r="75" spans="2:9" ht="15" customHeight="1">
       <c r="B75" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
@@ -2789,32 +2793,30 @@
       <c r="H75" s="21"/>
       <c r="I75" s="21"/>
     </row>
-    <row r="76" spans="2:8" ht="15" customHeight="1">
-      <c r="B76" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-    </row>
-    <row r="78" spans="2:8" ht="15" customHeight="1">
-      <c r="B78" s="13" t="s">
+    <row r="77" spans="2:8" ht="15" customHeight="1">
+      <c r="B77" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+    </row>
+    <row r="79" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B79" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
     </row>
     <row r="80" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B80" s="22" t="s">
-        <v>102</v>
-      </c>
+      <c r="B80" s="23"/>
       <c r="C80" s="23"/>
       <c r="D80" s="23"/>
       <c r="E80" s="23"/>
@@ -2858,18 +2860,20 @@
       <c r="G84" s="23"/>
       <c r="H84" s="23"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B85" s="23"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="23"/>
-      <c r="H85" s="23"/>
-    </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="13" t="s">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
+      <c r="B86" s="13" t="s">
         <v>103</v>
+      </c>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+    </row>
+    <row r="87" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B87" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="C87" s="21"/>
       <c r="D87" s="21"/>
@@ -2880,7 +2884,7 @@
     </row>
     <row r="88" spans="2:8" ht="27.6" customHeight="1">
       <c r="B88" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C88" s="21"/>
       <c r="D88" s="21"/>
@@ -2891,7 +2895,7 @@
     </row>
     <row r="89" spans="2:8" ht="27.6" customHeight="1">
       <c r="B89" s="24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C89" s="21"/>
       <c r="D89" s="21"/>
@@ -2900,37 +2904,25 @@
       <c r="G89" s="21"/>
       <c r="H89" s="21"/>
     </row>
-    <row r="90" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B90" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="C90" s="21"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="21"/>
-      <c r="G90" s="21"/>
-      <c r="H90" s="21"/>
-    </row>
-    <row r="93" ht="15">
-      <c r="B93" s="21" t="s">
+    <row r="92" ht="15">
+      <c r="B92" s="21" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="107" ht="15">
+      <c r="B107" s="21" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="108" ht="15">
       <c r="B108" s="21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="109" ht="15">
-      <c r="B109" s="21" t="s">
         <v>109</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="B78:H78"/>
-    <mergeCell ref="B80:H85"/>
+  <mergeCells count="10">
+    <mergeCell ref="B79:H84"/>
+    <mergeCell ref="B86:H86"/>
     <mergeCell ref="B87:H87"/>
     <mergeCell ref="B88:H88"/>
     <mergeCell ref="B89:H89"/>
@@ -2938,7 +2930,7 @@
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B75:I75"/>
-    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B77:H77"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
